--- a/danhsachkhachmoi.xlsx
+++ b/danhsachkhachmoi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\VinhPhuVinhPhuc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DBC5629-17A4-4C2D-8129-FBAD140168B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C41A09B1-E7FC-4052-81F8-EF59BB365C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
   <si>
     <t>STT</t>
   </si>
@@ -236,30 +236,9 @@
     <t>63</t>
   </si>
   <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
     <t>Đại lý Quyến Thắm</t>
   </si>
   <si>
-    <t>Đại lý Quyền Hương</t>
-  </si>
-  <si>
     <t>Đại lý Sâm Dung</t>
   </si>
   <si>
@@ -311,9 +290,6 @@
     <t>Đại lý Nguyễn Hoan</t>
   </si>
   <si>
-    <t>Đại lý Nhượng xuân</t>
-  </si>
-  <si>
     <t>Đại lý Nam Bình</t>
   </si>
   <si>
@@ -347,9 +323,6 @@
     <t>Đại lý Đình Túy</t>
   </si>
   <si>
-    <t>Đại lý Thắng Hân</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Trịnh Phượng  </t>
   </si>
   <si>
@@ -386,9 +359,6 @@
     <t>Đại lý Hiếu Nguyệt</t>
   </si>
   <si>
-    <t xml:space="preserve">Đại lý Bình Hằng </t>
-  </si>
-  <si>
     <t>Đại lý Thanh Quyết</t>
   </si>
   <si>
@@ -450,12 +420,6 @@
   </si>
   <si>
     <t>Đại lý Hưng Thu</t>
-  </si>
-  <si>
-    <t>Đại lý Thiêm Du</t>
-  </si>
-  <si>
-    <t>Đại lý Liên Anh</t>
   </si>
   <si>
     <t>Đại lý Tâm Hương</t>
@@ -499,7 +463,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -522,11 +486,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -544,6 +519,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -854,7 +832,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -865,7 +843,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -876,7 +854,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -887,7 +865,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -898,7 +876,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -909,7 +887,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -920,7 +898,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -931,7 +909,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -942,7 +920,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -953,7 +931,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -964,7 +942,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -975,7 +953,7 @@
         <v>14</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -986,7 +964,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -997,7 +975,7 @@
         <v>16</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1008,7 +986,7 @@
         <v>17</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1019,7 +997,7 @@
         <v>18</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1030,7 +1008,7 @@
         <v>19</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1041,7 +1019,7 @@
         <v>20</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1052,7 +1030,7 @@
         <v>21</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1063,7 +1041,7 @@
         <v>22</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1074,7 +1052,7 @@
         <v>23</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1085,7 +1063,7 @@
         <v>24</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1096,7 +1074,7 @@
         <v>25</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1107,7 +1085,7 @@
         <v>26</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1118,7 +1096,7 @@
         <v>27</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1129,7 +1107,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1140,7 +1118,7 @@
         <v>29</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1151,7 +1129,7 @@
         <v>30</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1162,7 +1140,7 @@
         <v>31</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -1173,7 +1151,7 @@
         <v>32</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1184,7 +1162,7 @@
         <v>33</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1195,7 +1173,7 @@
         <v>34</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1206,7 +1184,7 @@
         <v>35</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1217,7 +1195,7 @@
         <v>36</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -1228,7 +1206,7 @@
         <v>37</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1239,7 +1217,7 @@
         <v>38</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1250,7 +1228,7 @@
         <v>39</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -1261,7 +1239,7 @@
         <v>40</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1272,7 +1250,7 @@
         <v>41</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -1283,7 +1261,7 @@
         <v>42</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -1294,7 +1272,7 @@
         <v>43</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -1305,7 +1283,7 @@
         <v>44</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1316,7 +1294,7 @@
         <v>45</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -1327,7 +1305,7 @@
         <v>46</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1338,7 +1316,7 @@
         <v>47</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1349,7 +1327,7 @@
         <v>48</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -1360,7 +1338,7 @@
         <v>49</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1371,7 +1349,7 @@
         <v>50</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1382,7 +1360,7 @@
         <v>51</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1393,7 +1371,7 @@
         <v>52</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1404,7 +1382,7 @@
         <v>53</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1415,7 +1393,7 @@
         <v>54</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1426,7 +1404,7 @@
         <v>55</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1437,7 +1415,7 @@
         <v>56</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1448,7 +1426,7 @@
         <v>57</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1459,7 +1437,7 @@
         <v>58</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1470,7 +1448,7 @@
         <v>59</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1481,7 +1459,7 @@
         <v>60</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -1492,7 +1470,7 @@
         <v>61</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -1503,7 +1481,7 @@
         <v>62</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1514,7 +1492,7 @@
         <v>63</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1525,7 +1503,7 @@
         <v>64</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1536,74 +1514,33 @@
         <v>65</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="5">
-        <v>64</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>135</v>
-      </c>
+      <c r="A65"/>
+      <c r="B65"/>
+      <c r="C65" s="7"/>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="5">
-        <v>65</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>136</v>
-      </c>
+      <c r="A66"/>
+      <c r="B66"/>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="5">
-        <v>66</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>137</v>
-      </c>
+      <c r="A67"/>
+      <c r="B67"/>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="5">
-        <v>67</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="A68"/>
+      <c r="B68"/>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="5">
-        <v>68</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>139</v>
-      </c>
+      <c r="A69"/>
+      <c r="B69"/>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="5">
-        <v>69</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>140</v>
-      </c>
+      <c r="A70"/>
+      <c r="B70"/>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B71" s="2"/>

--- a/danhsachkhachmoi.xlsx
+++ b/danhsachkhachmoi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\VinhPhuVinhPhuc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C41A09B1-E7FC-4052-81F8-EF59BB365C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23131571-4863-4E9E-9022-87F383934C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
   <si>
     <t>STT</t>
   </si>
@@ -423,6 +423,12 @@
   </si>
   <si>
     <t>Đại lý Tâm Hương</t>
+  </si>
+  <si>
+    <t>Đại lý Hùng Phượng</t>
+  </si>
+  <si>
+    <t>Điện máy TC</t>
   </si>
 </sst>
 </file>
@@ -501,7 +507,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -522,6 +528,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1518,17 +1527,30 @@
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65"/>
-      <c r="B65"/>
-      <c r="C65" s="7"/>
+      <c r="A65" s="5">
+        <v>64</v>
+      </c>
+      <c r="B65" s="5">
+        <v>64</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66"/>
-      <c r="B66"/>
+      <c r="A66" s="5">
+        <v>65</v>
+      </c>
+      <c r="B66" s="5">
+        <v>65</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67"/>
-      <c r="B67"/>
+      <c r="B67" s="5"/>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68"/>
